--- a/backend/data/financials_by_company/0515.HK.xlsx
+++ b/backend/data/financials_by_company/0515.HK.xlsx
@@ -657,560 +657,560 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007296</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-28690000</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+        <v>2936000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>11053000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>11053000</v>
+      </c>
       <c r="G2" t="n">
-        <v>-52879000</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>-3936000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8713000</v>
+      </c>
       <c r="I2" t="n">
-        <v>38032000</v>
+        <v>353882000</v>
       </c>
       <c r="J2" t="n">
-        <v>-28690000</v>
+        <v>13989000</v>
       </c>
       <c r="K2" t="n">
-        <v>-28690000</v>
+        <v>5276000</v>
       </c>
       <c r="L2" t="n">
-        <v>-23768000</v>
+        <v>-10887000</v>
       </c>
       <c r="M2" t="n">
-        <v>25315000</v>
+        <v>11925000</v>
       </c>
       <c r="N2" t="n">
-        <v>1547000</v>
+        <v>1038000</v>
       </c>
       <c r="O2" t="n">
-        <v>-52879000</v>
+        <v>-14989000</v>
       </c>
       <c r="P2" t="n">
-        <v>-52879000</v>
+        <v>-3936000</v>
       </c>
       <c r="Q2" t="n">
-        <v>70119000</v>
+        <v>384198000</v>
       </c>
       <c r="R2" t="n">
-        <v>952389000</v>
+        <v>110379000</v>
       </c>
       <c r="S2" t="n">
-        <v>952389000</v>
+        <v>110379000</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0555</v>
+        <v>-0.0355</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0555</v>
+        <v>-0.0355</v>
       </c>
       <c r="V2" t="n">
-        <v>-52879000</v>
+        <v>-3936000</v>
       </c>
       <c r="W2" t="n">
-        <v>-52879000</v>
+        <v>-3936000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-52879000</v>
+        <v>-3936000</v>
       </c>
       <c r="Z2" t="n">
-        <v>732000</v>
+        <v>2713000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-53611000</v>
+        <v>-6649000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-53611000</v>
+        <v>-6649000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-394000</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-54005000</v>
+        <v>-6649000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-458000</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
+        <v>2711000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>11053000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-11053000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
       <c r="AI2" t="n">
-        <v>-23768000</v>
+        <v>-10887000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>25315000</v>
+        <v>11925000</v>
       </c>
       <c r="AK2" t="n">
-        <v>1547000</v>
+        <v>1038000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-29779000</v>
+        <v>-8823000</v>
       </c>
       <c r="AM2" t="n">
-        <v>32087000</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+        <v>30316000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-3733000</v>
+      </c>
       <c r="AO2" t="n">
-        <v>34780000</v>
+        <v>55077000</v>
       </c>
       <c r="AP2" t="n">
-        <v>2746000</v>
+        <v>16681000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>32034000</v>
+        <v>38396000</v>
       </c>
       <c r="AR2" t="n">
-        <v>2308000</v>
+        <v>21493000</v>
       </c>
       <c r="AS2" t="n">
-        <v>38032000</v>
+        <v>353882000</v>
       </c>
       <c r="AT2" t="n">
-        <v>40340000</v>
+        <v>375375000</v>
       </c>
       <c r="AU2" t="n">
-        <v>40340000</v>
+        <v>375375000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.011895</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-16158000</v>
+        <v>-18151000</v>
       </c>
       <c r="E3" t="n">
-        <v>2566000</v>
+        <v>-2424000</v>
       </c>
       <c r="F3" t="n">
-        <v>2566000</v>
+        <v>-2424000</v>
       </c>
       <c r="G3" t="n">
-        <v>-31043000</v>
+        <v>-41053000</v>
       </c>
       <c r="H3" t="n">
-        <v>10982000</v>
+        <v>7297000</v>
       </c>
       <c r="I3" t="n">
-        <v>242178000</v>
+        <v>241903000</v>
       </c>
       <c r="J3" t="n">
-        <v>-16158000</v>
+        <v>-20575000</v>
       </c>
       <c r="K3" t="n">
-        <v>-16158000</v>
+        <v>-27872000</v>
       </c>
       <c r="L3" t="n">
-        <v>-16571000</v>
+        <v>-14893000</v>
       </c>
       <c r="M3" t="n">
-        <v>17638000</v>
+        <v>15843000</v>
       </c>
       <c r="N3" t="n">
-        <v>1067000</v>
+        <v>950000</v>
       </c>
       <c r="O3" t="n">
-        <v>-31043000</v>
+        <v>-38629000</v>
       </c>
       <c r="P3" t="n">
-        <v>-31043000</v>
+        <v>-41053000</v>
       </c>
       <c r="Q3" t="n">
-        <v>290170000</v>
+        <v>288366000</v>
       </c>
       <c r="R3" t="n">
-        <v>133883000</v>
+        <v>128068600</v>
       </c>
       <c r="S3" t="n">
-        <v>133883000</v>
+        <v>128068600</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.232</v>
+        <v>-0.3205</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.232</v>
+        <v>-0.3205</v>
       </c>
       <c r="V3" t="n">
-        <v>-31043000</v>
+        <v>-41053000</v>
       </c>
       <c r="W3" t="n">
-        <v>-31043000</v>
+        <v>-41053000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-31043000</v>
+        <v>-41053000</v>
       </c>
       <c r="Z3" t="n">
-        <v>2351000</v>
+        <v>2662000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-33394000</v>
+        <v>-43715000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-33394000</v>
+        <v>-43715000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-402000</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-33796000</v>
+        <v>-43715000</v>
       </c>
       <c r="AE3" t="n">
-        <v>10811000</v>
+        <v>-101000</v>
       </c>
       <c r="AF3" t="n">
-        <v>2566000</v>
+        <v>-2424000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-2566000</v>
+        <v>297000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2127000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-16571000</v>
+        <v>-14893000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>17638000</v>
+        <v>15843000</v>
       </c>
       <c r="AK3" t="n">
-        <v>1067000</v>
+        <v>950000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-28036000</v>
+        <v>-28187000</v>
       </c>
       <c r="AM3" t="n">
-        <v>47992000</v>
+        <v>46463000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-2959000</v>
+        <v>-3927000</v>
       </c>
       <c r="AO3" t="n">
-        <v>51997000</v>
+        <v>53428000</v>
       </c>
       <c r="AP3" t="n">
-        <v>15119000</v>
+        <v>14488000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>36878000</v>
+        <v>38940000</v>
       </c>
       <c r="AR3" t="n">
-        <v>19956000</v>
+        <v>18276000</v>
       </c>
       <c r="AS3" t="n">
-        <v>242178000</v>
+        <v>241903000</v>
       </c>
       <c r="AT3" t="n">
-        <v>262134000</v>
+        <v>260179000</v>
       </c>
       <c r="AU3" t="n">
-        <v>262134000</v>
+        <v>260179000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.011895</v>
       </c>
       <c r="D4" t="n">
-        <v>-18151000</v>
+        <v>-16158000</v>
       </c>
       <c r="E4" t="n">
-        <v>-2424000</v>
+        <v>2566000</v>
       </c>
       <c r="F4" t="n">
-        <v>-2424000</v>
+        <v>2566000</v>
       </c>
       <c r="G4" t="n">
-        <v>-41053000</v>
+        <v>-31043000</v>
       </c>
       <c r="H4" t="n">
-        <v>7297000</v>
+        <v>10982000</v>
       </c>
       <c r="I4" t="n">
-        <v>241903000</v>
+        <v>242178000</v>
       </c>
       <c r="J4" t="n">
-        <v>-20575000</v>
+        <v>-16158000</v>
       </c>
       <c r="K4" t="n">
-        <v>-27872000</v>
+        <v>-16158000</v>
       </c>
       <c r="L4" t="n">
-        <v>-14893000</v>
+        <v>-16571000</v>
       </c>
       <c r="M4" t="n">
-        <v>15843000</v>
+        <v>17638000</v>
       </c>
       <c r="N4" t="n">
-        <v>950000</v>
+        <v>1067000</v>
       </c>
       <c r="O4" t="n">
-        <v>-38629000</v>
+        <v>-31043000</v>
       </c>
       <c r="P4" t="n">
-        <v>-41053000</v>
+        <v>-31043000</v>
       </c>
       <c r="Q4" t="n">
-        <v>288366000</v>
+        <v>290170000</v>
       </c>
       <c r="R4" t="n">
-        <v>128068600</v>
+        <v>133883000</v>
       </c>
       <c r="S4" t="n">
-        <v>128068600</v>
+        <v>133883000</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3205</v>
+        <v>-0.232</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3205</v>
+        <v>-0.232</v>
       </c>
       <c r="V4" t="n">
-        <v>-41053000</v>
+        <v>-31043000</v>
       </c>
       <c r="W4" t="n">
-        <v>-41053000</v>
+        <v>-31043000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-41053000</v>
+        <v>-31043000</v>
       </c>
       <c r="Z4" t="n">
-        <v>2662000</v>
+        <v>2351000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-43715000</v>
+        <v>-33394000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-43715000</v>
+        <v>-33394000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>-402000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-43715000</v>
+        <v>-33796000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-101000</v>
+        <v>10811000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-2424000</v>
+        <v>2566000</v>
       </c>
       <c r="AG4" t="n">
-        <v>297000</v>
+        <v>-2566000</v>
       </c>
       <c r="AH4" t="n">
-        <v>2127000</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>-14893000</v>
+        <v>-16571000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>15843000</v>
+        <v>17638000</v>
       </c>
       <c r="AK4" t="n">
-        <v>950000</v>
+        <v>1067000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-28187000</v>
+        <v>-28036000</v>
       </c>
       <c r="AM4" t="n">
-        <v>46463000</v>
+        <v>47992000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-3927000</v>
+        <v>-2959000</v>
       </c>
       <c r="AO4" t="n">
-        <v>53428000</v>
+        <v>51997000</v>
       </c>
       <c r="AP4" t="n">
-        <v>14488000</v>
+        <v>15119000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>38940000</v>
+        <v>36878000</v>
       </c>
       <c r="AR4" t="n">
-        <v>18276000</v>
+        <v>19956000</v>
       </c>
       <c r="AS4" t="n">
-        <v>241903000</v>
+        <v>242178000</v>
       </c>
       <c r="AT4" t="n">
-        <v>260179000</v>
+        <v>262134000</v>
       </c>
       <c r="AU4" t="n">
-        <v>260179000</v>
+        <v>262134000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.007296</v>
       </c>
       <c r="D5" t="n">
-        <v>2936000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>11053000</v>
-      </c>
-      <c r="F5" t="n">
-        <v>11053000</v>
-      </c>
+        <v>-28690000</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>-3936000</v>
-      </c>
-      <c r="H5" t="n">
-        <v>8713000</v>
-      </c>
+        <v>-52879000</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>353882000</v>
+        <v>38032000</v>
       </c>
       <c r="J5" t="n">
-        <v>13989000</v>
+        <v>-28690000</v>
       </c>
       <c r="K5" t="n">
-        <v>5276000</v>
+        <v>-28690000</v>
       </c>
       <c r="L5" t="n">
-        <v>-10887000</v>
+        <v>-23768000</v>
       </c>
       <c r="M5" t="n">
-        <v>11925000</v>
+        <v>25315000</v>
       </c>
       <c r="N5" t="n">
-        <v>1038000</v>
+        <v>1547000</v>
       </c>
       <c r="O5" t="n">
-        <v>-14989000</v>
+        <v>-52879000</v>
       </c>
       <c r="P5" t="n">
-        <v>-3936000</v>
+        <v>-52879000</v>
       </c>
       <c r="Q5" t="n">
-        <v>384198000</v>
+        <v>70119000</v>
       </c>
       <c r="R5" t="n">
-        <v>110379000</v>
+        <v>952389000</v>
       </c>
       <c r="S5" t="n">
-        <v>110379000</v>
+        <v>952389000</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0355</v>
+        <v>-0.0555</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0355</v>
+        <v>-0.0555</v>
       </c>
       <c r="V5" t="n">
-        <v>-3936000</v>
+        <v>-52879000</v>
       </c>
       <c r="W5" t="n">
-        <v>-3936000</v>
+        <v>-52879000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-3936000</v>
+        <v>-52879000</v>
       </c>
       <c r="Z5" t="n">
-        <v>2713000</v>
+        <v>732000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-6649000</v>
+        <v>-53611000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-6649000</v>
+        <v>-53611000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>-394000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-6649000</v>
+        <v>-54005000</v>
       </c>
       <c r="AE5" t="n">
-        <v>2711000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>11053000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-11053000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
+        <v>-458000</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>-10887000</v>
+        <v>-23768000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>11925000</v>
+        <v>25315000</v>
       </c>
       <c r="AK5" t="n">
-        <v>1038000</v>
+        <v>1547000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-8823000</v>
+        <v>-29779000</v>
       </c>
       <c r="AM5" t="n">
-        <v>30316000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-3733000</v>
-      </c>
+        <v>32087000</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>55077000</v>
+        <v>34780000</v>
       </c>
       <c r="AP5" t="n">
-        <v>16681000</v>
+        <v>2746000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>38396000</v>
+        <v>32034000</v>
       </c>
       <c r="AR5" t="n">
-        <v>21493000</v>
+        <v>2308000</v>
       </c>
       <c r="AS5" t="n">
-        <v>353882000</v>
+        <v>38032000</v>
       </c>
       <c r="AT5" t="n">
-        <v>375375000</v>
+        <v>40340000</v>
       </c>
       <c r="AU5" t="n">
-        <v>375375000</v>
+        <v>40340000</v>
       </c>
     </row>
   </sheetData>
@@ -1531,714 +1531,714 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>1133298394</v>
+        <v>557847394</v>
       </c>
       <c r="C2" t="n">
-        <v>226659678</v>
+        <v>111569478</v>
       </c>
       <c r="D2" t="n">
-        <v>303615000</v>
+        <v>136410000</v>
       </c>
       <c r="E2" t="n">
-        <v>308784000</v>
+        <v>156995000</v>
       </c>
       <c r="F2" t="n">
-        <v>61273000</v>
+        <v>44073000</v>
       </c>
       <c r="G2" t="n">
-        <v>369515000</v>
+        <v>216151000</v>
       </c>
       <c r="H2" t="n">
-        <v>-542131000</v>
+        <v>-232129000</v>
       </c>
       <c r="I2" t="n">
-        <v>61273000</v>
+        <v>44073000</v>
       </c>
       <c r="J2" t="n">
-        <v>542000</v>
+        <v>685000</v>
       </c>
       <c r="K2" t="n">
-        <v>61273000</v>
+        <v>59841000</v>
       </c>
       <c r="L2" t="n">
-        <v>73480000</v>
+        <v>59841000</v>
       </c>
       <c r="M2" t="n">
-        <v>-1743000</v>
+        <v>492000</v>
       </c>
       <c r="N2" t="n">
-        <v>-63016000</v>
+        <v>-59349000</v>
       </c>
       <c r="O2" t="n">
-        <v>61273000</v>
+        <v>59841000</v>
       </c>
       <c r="P2" t="n">
-        <v>9794000</v>
+        <v>11313000</v>
       </c>
       <c r="Q2" t="n">
-        <v>55670000</v>
+        <v>52621000</v>
       </c>
       <c r="R2" t="n">
-        <v>-96637000</v>
+        <v>-883405000</v>
       </c>
       <c r="S2" t="n">
-        <v>46346000</v>
+        <v>568181000</v>
       </c>
       <c r="T2" t="n">
-        <v>1133000</v>
+        <v>278924000</v>
       </c>
       <c r="U2" t="n">
-        <v>1133000</v>
+        <v>278924000</v>
       </c>
       <c r="V2" t="n">
-        <v>679920000</v>
+        <v>551426000</v>
       </c>
       <c r="W2" t="n">
-        <v>31906000</v>
+        <v>18177000</v>
       </c>
       <c r="X2" t="n">
-        <v>19699000</v>
+        <v>18177000</v>
       </c>
       <c r="Y2" t="n">
-        <v>12207000</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
-      <c r="AA2" t="n">
-        <v>12207000</v>
-      </c>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>648014000</v>
+        <v>533249000</v>
       </c>
       <c r="AC2" t="n">
-        <v>296577000</v>
+        <v>156995000</v>
       </c>
       <c r="AD2" t="n">
-        <v>542000</v>
+        <v>685000</v>
       </c>
       <c r="AE2" t="n">
-        <v>296035000</v>
+        <v>156310000</v>
       </c>
       <c r="AF2" t="n">
-        <v>340366000</v>
+        <v>350516000</v>
       </c>
       <c r="AG2" t="n">
-        <v>154218000</v>
+        <v>23900000</v>
       </c>
       <c r="AH2" t="n">
-        <v>68016000</v>
+        <v>67747000</v>
       </c>
       <c r="AI2" t="n">
-        <v>118132000</v>
+        <v>258869000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>678177000</v>
+        <v>551918000</v>
       </c>
       <c r="AK2" t="n">
-        <v>572294000</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
+        <v>250798000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>15768000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>15768000</v>
+      </c>
       <c r="AN2" t="n">
-        <v>572294000</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
+        <v>235030000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>-353605000</v>
+      </c>
       <c r="AP2" t="n">
-        <v>572294000</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
+        <v>588635000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>82173000</v>
+      </c>
       <c r="AR2" t="n">
-        <v>572294000</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
+        <v>250798000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>262046000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>244416000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
       <c r="AV2" t="n">
-        <v>105883000</v>
+        <v>301120000</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>50775000</v>
       </c>
       <c r="AX2" t="n">
-        <v>20506000</v>
+        <v>3668000</v>
       </c>
       <c r="AY2" t="n">
-        <v>27463000</v>
-      </c>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
+        <v>49391000</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>16744000</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>10887000</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>21760000</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>43197000</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1066000</v>
+      </c>
       <c r="BE2" t="n">
-        <v>53287000</v>
+        <v>133123000</v>
       </c>
       <c r="BF2" t="n">
-        <v>-93960000</v>
+        <v>-91084000</v>
       </c>
       <c r="BG2" t="n">
-        <v>147247000</v>
+        <v>224207000</v>
       </c>
       <c r="BH2" t="n">
-        <v>4627000</v>
+        <v>19900000</v>
       </c>
       <c r="BI2" t="n">
-        <v>4627000</v>
+        <v>19900000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>669415394</v>
+        <v>669415000</v>
       </c>
       <c r="C3" t="n">
-        <v>133883078</v>
+        <v>133883000</v>
       </c>
       <c r="D3" t="n">
-        <v>300108000</v>
+        <v>282828000</v>
       </c>
       <c r="E3" t="n">
-        <v>310500000</v>
+        <v>313462000</v>
       </c>
       <c r="F3" t="n">
-        <v>50783000</v>
+        <v>64578000</v>
       </c>
       <c r="G3" t="n">
-        <v>374423000</v>
+        <v>391022000</v>
       </c>
       <c r="H3" t="n">
-        <v>-496570000</v>
+        <v>-408416000</v>
       </c>
       <c r="I3" t="n">
-        <v>50783000</v>
+        <v>64578000</v>
       </c>
       <c r="J3" t="n">
+        <v>2171000</v>
+      </c>
+      <c r="K3" t="n">
+        <v>79731000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>79731000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>18794000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-60937000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>79731000</v>
+      </c>
+      <c r="P3" t="n">
+        <v>11313000</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>53425000</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-924458000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>568181000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>334708000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>334708000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>686586000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>19843000</v>
+      </c>
+      <c r="X3" t="n">
+        <v>18445000</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1398000</v>
       </c>
-      <c r="K3" t="n">
-        <v>65321000</v>
-      </c>
-      <c r="L3" t="n">
-        <v>75141000</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2993000</v>
-      </c>
-      <c r="N3" t="n">
-        <v>-62328000</v>
-      </c>
-      <c r="O3" t="n">
-        <v>65321000</v>
-      </c>
-      <c r="P3" t="n">
-        <v>18793000</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>55196000</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-53751000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>470000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>669000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>669000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>697102000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>30297000</v>
-      </c>
-      <c r="X3" t="n">
-        <v>19935000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>10362000</v>
-      </c>
       <c r="Z3" t="n">
-        <v>542000</v>
+        <v>1398000</v>
       </c>
       <c r="AA3" t="n">
-        <v>9820000</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>666805000</v>
+        <v>666743000</v>
       </c>
       <c r="AC3" t="n">
-        <v>300138000</v>
+        <v>312064000</v>
       </c>
       <c r="AD3" t="n">
-        <v>856000</v>
+        <v>773000</v>
       </c>
       <c r="AE3" t="n">
-        <v>299282000</v>
+        <v>311291000</v>
       </c>
       <c r="AF3" t="n">
-        <v>354931000</v>
+        <v>341664000</v>
       </c>
       <c r="AG3" t="n">
-        <v>122621000</v>
+        <v>70289000</v>
       </c>
       <c r="AH3" t="n">
-        <v>67344000</v>
+        <v>65737000</v>
       </c>
       <c r="AI3" t="n">
-        <v>164966000</v>
+        <v>205638000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>700095000</v>
+        <v>705380000</v>
       </c>
       <c r="AK3" t="n">
-        <v>529860000</v>
+        <v>447053000</v>
       </c>
       <c r="AL3" t="n">
-        <v>14538000</v>
+        <v>15153000</v>
       </c>
       <c r="AM3" t="n">
-        <v>14538000</v>
+        <v>15153000</v>
       </c>
       <c r="AN3" t="n">
-        <v>515322000</v>
+        <v>431900000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-171951000</v>
+        <v>-194484000</v>
       </c>
       <c r="AP3" t="n">
-        <v>687273000</v>
+        <v>626384000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>317317000</v>
-      </c>
-      <c r="AR3" t="inlineStr"/>
+        <v>287593000</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>447053000</v>
+      </c>
       <c r="AS3" t="n">
-        <v>124191000</v>
+        <v>95763000</v>
       </c>
       <c r="AT3" t="n">
-        <v>245765000</v>
+        <v>243028000</v>
       </c>
       <c r="AU3" t="n">
         <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>170235000</v>
+        <v>258327000</v>
       </c>
       <c r="AW3" t="n">
-        <v>40714000</v>
+        <v>46700000</v>
       </c>
       <c r="AX3" t="n">
-        <v>12138000</v>
+        <v>12116000</v>
       </c>
       <c r="AY3" t="n">
-        <v>33693000</v>
+        <v>46266000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>7426000</v>
+        <v>20307000</v>
       </c>
       <c r="BA3" t="n">
-        <v>8867000</v>
+        <v>12167000</v>
       </c>
       <c r="BB3" t="n">
-        <v>17400000</v>
+        <v>13792000</v>
       </c>
       <c r="BC3" t="n">
-        <v>11530000</v>
+        <v>30519000</v>
       </c>
       <c r="BD3" t="n">
-        <v>2175000</v>
+        <v>1155000</v>
       </c>
       <c r="BE3" t="n">
-        <v>60991000</v>
+        <v>93108000</v>
       </c>
       <c r="BF3" t="n">
-        <v>-93960000</v>
+        <v>-91132000</v>
       </c>
       <c r="BG3" t="n">
-        <v>154951000</v>
+        <v>184240000</v>
       </c>
       <c r="BH3" t="n">
-        <v>8994000</v>
+        <v>28463000</v>
       </c>
       <c r="BI3" t="n">
-        <v>8994000</v>
+        <v>28463000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>669415000</v>
+        <v>669415394</v>
       </c>
       <c r="C4" t="n">
-        <v>133883000</v>
+        <v>133883078</v>
       </c>
       <c r="D4" t="n">
-        <v>282828000</v>
+        <v>300108000</v>
       </c>
       <c r="E4" t="n">
-        <v>313462000</v>
+        <v>310500000</v>
       </c>
       <c r="F4" t="n">
-        <v>64578000</v>
+        <v>50783000</v>
       </c>
       <c r="G4" t="n">
-        <v>391022000</v>
+        <v>374423000</v>
       </c>
       <c r="H4" t="n">
-        <v>-408416000</v>
+        <v>-496570000</v>
       </c>
       <c r="I4" t="n">
-        <v>64578000</v>
+        <v>50783000</v>
       </c>
       <c r="J4" t="n">
-        <v>2171000</v>
+        <v>1398000</v>
       </c>
       <c r="K4" t="n">
-        <v>79731000</v>
+        <v>65321000</v>
       </c>
       <c r="L4" t="n">
-        <v>79731000</v>
+        <v>75141000</v>
       </c>
       <c r="M4" t="n">
-        <v>18794000</v>
+        <v>2993000</v>
       </c>
       <c r="N4" t="n">
-        <v>-60937000</v>
+        <v>-62328000</v>
       </c>
       <c r="O4" t="n">
-        <v>79731000</v>
+        <v>65321000</v>
       </c>
       <c r="P4" t="n">
-        <v>11313000</v>
+        <v>18793000</v>
       </c>
       <c r="Q4" t="n">
-        <v>53425000</v>
+        <v>55196000</v>
       </c>
       <c r="R4" t="n">
-        <v>-924458000</v>
+        <v>-53751000</v>
       </c>
       <c r="S4" t="n">
-        <v>568181000</v>
+        <v>470000</v>
       </c>
       <c r="T4" t="n">
-        <v>334708000</v>
+        <v>669000</v>
       </c>
       <c r="U4" t="n">
-        <v>334708000</v>
+        <v>669000</v>
       </c>
       <c r="V4" t="n">
-        <v>686586000</v>
+        <v>697102000</v>
       </c>
       <c r="W4" t="n">
-        <v>19843000</v>
+        <v>30297000</v>
       </c>
       <c r="X4" t="n">
-        <v>18445000</v>
+        <v>19935000</v>
       </c>
       <c r="Y4" t="n">
-        <v>1398000</v>
+        <v>10362000</v>
       </c>
       <c r="Z4" t="n">
-        <v>1398000</v>
+        <v>542000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>9820000</v>
       </c>
       <c r="AB4" t="n">
-        <v>666743000</v>
+        <v>666805000</v>
       </c>
       <c r="AC4" t="n">
-        <v>312064000</v>
+        <v>300138000</v>
       </c>
       <c r="AD4" t="n">
-        <v>773000</v>
+        <v>856000</v>
       </c>
       <c r="AE4" t="n">
-        <v>311291000</v>
+        <v>299282000</v>
       </c>
       <c r="AF4" t="n">
-        <v>341664000</v>
+        <v>354931000</v>
       </c>
       <c r="AG4" t="n">
-        <v>70289000</v>
+        <v>122621000</v>
       </c>
       <c r="AH4" t="n">
-        <v>65737000</v>
+        <v>67344000</v>
       </c>
       <c r="AI4" t="n">
-        <v>205638000</v>
+        <v>164966000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>705380000</v>
+        <v>700095000</v>
       </c>
       <c r="AK4" t="n">
-        <v>447053000</v>
+        <v>529860000</v>
       </c>
       <c r="AL4" t="n">
-        <v>15153000</v>
+        <v>14538000</v>
       </c>
       <c r="AM4" t="n">
-        <v>15153000</v>
+        <v>14538000</v>
       </c>
       <c r="AN4" t="n">
-        <v>431900000</v>
+        <v>515322000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-194484000</v>
+        <v>-171951000</v>
       </c>
       <c r="AP4" t="n">
-        <v>626384000</v>
+        <v>687273000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>287593000</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>447053000</v>
-      </c>
+        <v>317317000</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>95763000</v>
+        <v>124191000</v>
       </c>
       <c r="AT4" t="n">
-        <v>243028000</v>
+        <v>245765000</v>
       </c>
       <c r="AU4" t="n">
         <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>258327000</v>
+        <v>170235000</v>
       </c>
       <c r="AW4" t="n">
-        <v>46700000</v>
+        <v>40714000</v>
       </c>
       <c r="AX4" t="n">
-        <v>12116000</v>
+        <v>12138000</v>
       </c>
       <c r="AY4" t="n">
-        <v>46266000</v>
+        <v>33693000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>20307000</v>
+        <v>7426000</v>
       </c>
       <c r="BA4" t="n">
-        <v>12167000</v>
+        <v>8867000</v>
       </c>
       <c r="BB4" t="n">
-        <v>13792000</v>
+        <v>17400000</v>
       </c>
       <c r="BC4" t="n">
-        <v>30519000</v>
+        <v>11530000</v>
       </c>
       <c r="BD4" t="n">
-        <v>1155000</v>
+        <v>2175000</v>
       </c>
       <c r="BE4" t="n">
-        <v>93108000</v>
+        <v>60991000</v>
       </c>
       <c r="BF4" t="n">
-        <v>-91132000</v>
+        <v>-93960000</v>
       </c>
       <c r="BG4" t="n">
-        <v>184240000</v>
+        <v>154951000</v>
       </c>
       <c r="BH4" t="n">
-        <v>28463000</v>
+        <v>8994000</v>
       </c>
       <c r="BI4" t="n">
-        <v>28463000</v>
+        <v>8994000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>557847394</v>
+        <v>1133298394</v>
       </c>
       <c r="C5" t="n">
-        <v>111569478</v>
+        <v>226659678</v>
       </c>
       <c r="D5" t="n">
-        <v>136410000</v>
+        <v>303615000</v>
       </c>
       <c r="E5" t="n">
-        <v>156995000</v>
+        <v>308784000</v>
       </c>
       <c r="F5" t="n">
-        <v>44073000</v>
+        <v>61273000</v>
       </c>
       <c r="G5" t="n">
-        <v>216151000</v>
+        <v>369515000</v>
       </c>
       <c r="H5" t="n">
-        <v>-232129000</v>
+        <v>-542131000</v>
       </c>
       <c r="I5" t="n">
-        <v>44073000</v>
+        <v>61273000</v>
       </c>
       <c r="J5" t="n">
-        <v>685000</v>
+        <v>542000</v>
       </c>
       <c r="K5" t="n">
-        <v>59841000</v>
+        <v>61273000</v>
       </c>
       <c r="L5" t="n">
-        <v>59841000</v>
+        <v>73480000</v>
       </c>
       <c r="M5" t="n">
-        <v>492000</v>
+        <v>-1743000</v>
       </c>
       <c r="N5" t="n">
-        <v>-59349000</v>
+        <v>-63016000</v>
       </c>
       <c r="O5" t="n">
-        <v>59841000</v>
+        <v>61273000</v>
       </c>
       <c r="P5" t="n">
-        <v>11313000</v>
+        <v>9794000</v>
       </c>
       <c r="Q5" t="n">
-        <v>52621000</v>
+        <v>55670000</v>
       </c>
       <c r="R5" t="n">
-        <v>-883405000</v>
+        <v>-96637000</v>
       </c>
       <c r="S5" t="n">
-        <v>568181000</v>
+        <v>46346000</v>
       </c>
       <c r="T5" t="n">
-        <v>278924000</v>
+        <v>1133000</v>
       </c>
       <c r="U5" t="n">
-        <v>278924000</v>
+        <v>1133000</v>
       </c>
       <c r="V5" t="n">
-        <v>551426000</v>
+        <v>679920000</v>
       </c>
       <c r="W5" t="n">
-        <v>18177000</v>
+        <v>31906000</v>
       </c>
       <c r="X5" t="n">
-        <v>18177000</v>
+        <v>19699000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>12207000</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" t="inlineStr"/>
+      <c r="AA5" t="n">
+        <v>12207000</v>
+      </c>
       <c r="AB5" t="n">
-        <v>533249000</v>
+        <v>648014000</v>
       </c>
       <c r="AC5" t="n">
-        <v>156995000</v>
+        <v>296577000</v>
       </c>
       <c r="AD5" t="n">
-        <v>685000</v>
+        <v>542000</v>
       </c>
       <c r="AE5" t="n">
-        <v>156310000</v>
+        <v>296035000</v>
       </c>
       <c r="AF5" t="n">
-        <v>350516000</v>
+        <v>340366000</v>
       </c>
       <c r="AG5" t="n">
-        <v>23900000</v>
+        <v>154218000</v>
       </c>
       <c r="AH5" t="n">
-        <v>67747000</v>
+        <v>68016000</v>
       </c>
       <c r="AI5" t="n">
-        <v>258869000</v>
+        <v>118132000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>551918000</v>
+        <v>678177000</v>
       </c>
       <c r="AK5" t="n">
-        <v>250798000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>15768000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>15768000</v>
-      </c>
+        <v>572294000</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>235030000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>-353605000</v>
-      </c>
+        <v>572294000</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>588635000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>82173000</v>
-      </c>
+        <v>572294000</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="n">
-        <v>250798000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>262046000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>244416000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
+        <v>572294000</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>301120000</v>
+        <v>105883000</v>
       </c>
       <c r="AW5" t="n">
-        <v>50775000</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>3668000</v>
+        <v>20506000</v>
       </c>
       <c r="AY5" t="n">
-        <v>49391000</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>16744000</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>10887000</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>21760000</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>43197000</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>1066000</v>
-      </c>
+        <v>27463000</v>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="n">
-        <v>133123000</v>
+        <v>53287000</v>
       </c>
       <c r="BF5" t="n">
-        <v>-91084000</v>
+        <v>-93960000</v>
       </c>
       <c r="BG5" t="n">
-        <v>224207000</v>
+        <v>147247000</v>
       </c>
       <c r="BH5" t="n">
-        <v>19900000</v>
+        <v>4627000</v>
       </c>
       <c r="BI5" t="n">
-        <v>19900000</v>
+        <v>4627000</v>
       </c>
     </row>
   </sheetData>
@@ -2459,469 +2459,469 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-73365000</v>
+        <v>-8794000</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-156548000</v>
       </c>
       <c r="D2" t="n">
-        <v>3088000</v>
+        <v>159881000</v>
       </c>
       <c r="E2" t="n">
-        <v>46340000</v>
+        <v>7100000</v>
       </c>
       <c r="F2" t="n">
-        <v>-54124000</v>
+        <v>-82173000</v>
       </c>
       <c r="G2" t="n">
-        <v>4627000</v>
+        <v>19900000</v>
       </c>
       <c r="H2" t="n">
-        <v>8994000</v>
+        <v>25114000</v>
       </c>
       <c r="I2" t="n">
-        <v>-128000</v>
+        <v>423000</v>
       </c>
       <c r="J2" t="n">
-        <v>-4239000</v>
+        <v>-5637000</v>
       </c>
       <c r="K2" t="n">
-        <v>26865000</v>
+        <v>-2605000</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>-21707000</v>
+        <v>-11838000</v>
       </c>
       <c r="N2" t="n">
-        <v>46340000</v>
+        <v>7100000</v>
       </c>
       <c r="O2" t="n">
-        <v>46340000</v>
+        <v>7100000</v>
       </c>
       <c r="P2" t="n">
-        <v>3088000</v>
+        <v>3333000</v>
       </c>
       <c r="Q2" t="n">
-        <v>3088000</v>
+        <v>1548000</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-154762000</v>
       </c>
       <c r="S2" t="n">
-        <v>3088000</v>
+        <v>156310000</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1785000</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-1786000</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>3571000</v>
       </c>
       <c r="W2" t="n">
-        <v>-11863000</v>
+        <v>-76411000</v>
       </c>
       <c r="X2" t="n">
-        <v>42261000</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+        <v>-8501000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>608000</v>
+      </c>
       <c r="Z2" t="n">
-        <v>-54124000</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
+        <v>-68518000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>13655000</v>
+      </c>
       <c r="AB2" t="n">
-        <v>-54124000</v>
+        <v>-82173000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-19241000</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
+        <v>73379000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>75214000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-2674000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>22700000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-11338000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>66526000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>10887000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>-3733000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>8713000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>8713000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-11053000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>-6649000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-31316000</v>
+        <v>-196067000</v>
       </c>
       <c r="C3" t="n">
-        <v>-315942000</v>
+        <v>-159881000</v>
       </c>
       <c r="D3" t="n">
-        <v>336766000</v>
+        <v>315942000</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>55784000</v>
       </c>
       <c r="F3" t="n">
-        <v>-91428000</v>
+        <v>-209785000</v>
       </c>
       <c r="G3" t="n">
-        <v>8994000</v>
+        <v>28463000</v>
       </c>
       <c r="H3" t="n">
-        <v>28463000</v>
+        <v>19900000</v>
       </c>
       <c r="I3" t="n">
-        <v>-689000</v>
+        <v>-1427000</v>
       </c>
       <c r="J3" t="n">
-        <v>-18780000</v>
+        <v>9990000</v>
       </c>
       <c r="K3" t="n">
-        <v>4591000</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+        <v>195587000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>570000</v>
+      </c>
       <c r="M3" t="n">
-        <v>-15198000</v>
+        <v>-15727000</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>55784000</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>55784000</v>
       </c>
       <c r="P3" t="n">
-        <v>20824000</v>
+        <v>156061000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-12009000</v>
+        <v>154981000</v>
       </c>
       <c r="R3" t="n">
-        <v>-311291000</v>
+        <v>-156310000</v>
       </c>
       <c r="S3" t="n">
-        <v>299282000</v>
+        <v>311291000</v>
       </c>
       <c r="T3" t="n">
-        <v>32833000</v>
+        <v>1080000</v>
       </c>
       <c r="U3" t="n">
-        <v>-4651000</v>
+        <v>-3571000</v>
       </c>
       <c r="V3" t="n">
-        <v>37484000</v>
+        <v>4651000</v>
       </c>
       <c r="W3" t="n">
-        <v>-83483000</v>
+        <v>-199315000</v>
       </c>
       <c r="X3" t="n">
-        <v>7945000</v>
+        <v>2460000</v>
       </c>
       <c r="Y3" t="n">
-        <v>1067000</v>
+        <v>658000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-91428000</v>
+        <v>-202433000</v>
       </c>
       <c r="AA3" t="n">
-        <v>2566000</v>
+        <v>7352000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-91428000</v>
+        <v>-209785000</v>
       </c>
       <c r="AC3" t="n">
-        <v>60112000</v>
+        <v>13718000</v>
       </c>
       <c r="AD3" t="n">
-        <v>70718000</v>
+        <v>36746000</v>
       </c>
       <c r="AE3" t="n">
-        <v>2309000</v>
+        <v>-10596000</v>
       </c>
       <c r="AF3" t="n">
-        <v>8423000</v>
+        <v>8382000</v>
       </c>
       <c r="AG3" t="n">
-        <v>11006000</v>
+        <v>326000</v>
       </c>
       <c r="AH3" t="n">
-        <v>48980000</v>
+        <v>38634000</v>
       </c>
       <c r="AI3" t="n">
-        <v>16571000</v>
+        <v>14893000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1162000</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-2959000</v>
+        <v>-3927000</v>
       </c>
       <c r="AL3" t="n">
-        <v>10982000</v>
+        <v>7297000</v>
       </c>
       <c r="AM3" t="n">
-        <v>10982000</v>
+        <v>7297000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-2566000</v>
+        <v>297000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-33796000</v>
+        <v>-43715000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-196067000</v>
+        <v>-31316000</v>
       </c>
       <c r="C4" t="n">
-        <v>-159881000</v>
+        <v>-315942000</v>
       </c>
       <c r="D4" t="n">
-        <v>315942000</v>
+        <v>336766000</v>
       </c>
       <c r="E4" t="n">
-        <v>55784000</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-209785000</v>
+        <v>-91428000</v>
       </c>
       <c r="G4" t="n">
+        <v>8994000</v>
+      </c>
+      <c r="H4" t="n">
         <v>28463000</v>
       </c>
-      <c r="H4" t="n">
-        <v>19900000</v>
-      </c>
       <c r="I4" t="n">
-        <v>-1427000</v>
+        <v>-689000</v>
       </c>
       <c r="J4" t="n">
-        <v>9990000</v>
+        <v>-18780000</v>
       </c>
       <c r="K4" t="n">
-        <v>195587000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>570000</v>
-      </c>
+        <v>4591000</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>-15727000</v>
+        <v>-15198000</v>
       </c>
       <c r="N4" t="n">
-        <v>55784000</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>55784000</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>156061000</v>
+        <v>20824000</v>
       </c>
       <c r="Q4" t="n">
-        <v>154981000</v>
+        <v>-12009000</v>
       </c>
       <c r="R4" t="n">
-        <v>-156310000</v>
+        <v>-311291000</v>
       </c>
       <c r="S4" t="n">
-        <v>311291000</v>
+        <v>299282000</v>
       </c>
       <c r="T4" t="n">
-        <v>1080000</v>
+        <v>32833000</v>
       </c>
       <c r="U4" t="n">
-        <v>-3571000</v>
+        <v>-4651000</v>
       </c>
       <c r="V4" t="n">
-        <v>4651000</v>
+        <v>37484000</v>
       </c>
       <c r="W4" t="n">
-        <v>-199315000</v>
+        <v>-83483000</v>
       </c>
       <c r="X4" t="n">
-        <v>2460000</v>
+        <v>7945000</v>
       </c>
       <c r="Y4" t="n">
-        <v>658000</v>
+        <v>1067000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-202433000</v>
+        <v>-91428000</v>
       </c>
       <c r="AA4" t="n">
-        <v>7352000</v>
+        <v>2566000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-209785000</v>
+        <v>-91428000</v>
       </c>
       <c r="AC4" t="n">
-        <v>13718000</v>
+        <v>60112000</v>
       </c>
       <c r="AD4" t="n">
-        <v>36746000</v>
+        <v>70718000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-10596000</v>
+        <v>2309000</v>
       </c>
       <c r="AF4" t="n">
-        <v>8382000</v>
+        <v>8423000</v>
       </c>
       <c r="AG4" t="n">
-        <v>326000</v>
+        <v>11006000</v>
       </c>
       <c r="AH4" t="n">
-        <v>38634000</v>
+        <v>48980000</v>
       </c>
       <c r="AI4" t="n">
-        <v>14893000</v>
+        <v>16571000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1162000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-3927000</v>
+        <v>-2959000</v>
       </c>
       <c r="AL4" t="n">
-        <v>7297000</v>
+        <v>10982000</v>
       </c>
       <c r="AM4" t="n">
-        <v>7297000</v>
+        <v>10982000</v>
       </c>
       <c r="AN4" t="n">
-        <v>297000</v>
+        <v>-2566000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-43715000</v>
+        <v>-33796000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-8794000</v>
+        <v>-73365000</v>
       </c>
       <c r="C5" t="n">
-        <v>-156548000</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>159881000</v>
+        <v>3088000</v>
       </c>
       <c r="E5" t="n">
-        <v>7100000</v>
+        <v>46340000</v>
       </c>
       <c r="F5" t="n">
-        <v>-82173000</v>
+        <v>-54124000</v>
       </c>
       <c r="G5" t="n">
-        <v>19900000</v>
+        <v>4627000</v>
       </c>
       <c r="H5" t="n">
-        <v>25114000</v>
+        <v>8994000</v>
       </c>
       <c r="I5" t="n">
-        <v>423000</v>
+        <v>-128000</v>
       </c>
       <c r="J5" t="n">
-        <v>-5637000</v>
+        <v>-4239000</v>
       </c>
       <c r="K5" t="n">
-        <v>-2605000</v>
+        <v>26865000</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>-11838000</v>
+        <v>-21707000</v>
       </c>
       <c r="N5" t="n">
-        <v>7100000</v>
+        <v>46340000</v>
       </c>
       <c r="O5" t="n">
-        <v>7100000</v>
+        <v>46340000</v>
       </c>
       <c r="P5" t="n">
-        <v>3333000</v>
+        <v>3088000</v>
       </c>
       <c r="Q5" t="n">
-        <v>1548000</v>
+        <v>3088000</v>
       </c>
       <c r="R5" t="n">
-        <v>-154762000</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>156310000</v>
+        <v>3088000</v>
       </c>
       <c r="T5" t="n">
-        <v>1785000</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-1786000</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>3571000</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-76411000</v>
+        <v>-11863000</v>
       </c>
       <c r="X5" t="n">
-        <v>-8501000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>608000</v>
-      </c>
+        <v>42261000</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>-68518000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>13655000</v>
-      </c>
+        <v>-54124000</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>-82173000</v>
+        <v>-54124000</v>
       </c>
       <c r="AC5" t="n">
-        <v>73379000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>75214000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-2674000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>22700000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-11338000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>66526000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>10887000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>-3733000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>8713000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>8713000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-11053000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>-6649000</v>
-      </c>
+        <v>-19241000</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3450,187 +3450,187 @@
       </c>
       <c r="CY1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>longName</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
         </is>
       </c>
       <c r="EJ1" t="inlineStr">
@@ -3766,7 +3766,7 @@
         <v>3.19</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.8</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="AG2" t="n">
         <v>3226000</v>
@@ -3802,10 +3802,10 @@
         <v>49403197</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.172</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.5</v>
+        <v>0.71</v>
       </c>
       <c r="AT2" t="n">
         <v>67.09677000000001</v>
@@ -3820,7 +3820,7 @@
         <v>0.173</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.18267</v>
+        <v>0.175135</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -3893,10 +3893,10 @@
         <v>-13.682</v>
       </c>
       <c r="BU2" t="n">
-        <v>-0.91761905</v>
+        <v>-0.3346154</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BW2" t="n">
         <v>0.300209</v>
@@ -4000,140 +4000,140 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CY2" t="b">
-        <v>0</v>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="CZ2" t="n">
+        <v>1759219682</v>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>finmb_27313916</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DE2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI2" t="n">
         <v>1151026200000</v>
       </c>
-      <c r="DA2" t="n">
+      <c r="DJ2" t="n">
         <v>-0.00500001</v>
       </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DK2" t="inlineStr">
         <is>
           <t>0.173 - 0.184</t>
         </is>
       </c>
-      <c r="DC2" t="inlineStr">
+      <c r="DL2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>0.10199999</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>1.4366195</v>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>0.071 - 2.5</t>
-        </is>
-      </c>
-      <c r="DH2" t="n">
-        <v>-2.327</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>-0.93079996</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>-91.7619</v>
-      </c>
-      <c r="DK2" t="n">
+      <c r="DM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>0.0009999871</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>0.0058138785</v>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>0.172 - 0.71</t>
+        </is>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-0.537</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-0.75633806</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>-33.46154</v>
+      </c>
+      <c r="DT2" t="n">
         <v>1756378740</v>
       </c>
-      <c r="DL2" t="n">
+      <c r="DU2" t="n">
         <v>1756728000</v>
       </c>
-      <c r="DM2" t="b">
+      <c r="DV2" t="b">
         <v>1</v>
       </c>
-      <c r="DN2" t="n">
+      <c r="DW2" t="n">
         <v>-0.28</v>
       </c>
-      <c r="DO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>-0.009670003999999999</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>-0.052937016</v>
-      </c>
-      <c r="DS2" t="n">
+      <c r="DX2" t="n">
+        <v>-2.8089945</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>-0.0021350086</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>-0.012190645</v>
+      </c>
+      <c r="ED2" t="n">
         <v>15</v>
       </c>
-      <c r="DT2" t="n">
+      <c r="EE2" t="n">
         <v>15</v>
       </c>
-      <c r="DU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DW2" t="inlineStr">
+      <c r="EF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EG2" t="inlineStr">
         <is>
           <t>PREPRE</t>
         </is>
       </c>
-      <c r="DX2" t="n">
-        <v>0.173</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>1759219682</v>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>finmb_27313916</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="ED2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="EF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EG2" t="inlineStr">
+      <c r="EH2" t="inlineStr">
         <is>
           <t>CHINASILVER TEC</t>
         </is>
       </c>
-      <c r="EH2" t="inlineStr">
+      <c r="EI2" t="inlineStr">
         <is>
           <t>China Silver Technology Holdings Limited</t>
         </is>
-      </c>
-      <c r="EI2" t="n">
-        <v>-2.8089945</v>
       </c>
       <c r="EJ2" t="inlineStr"/>
     </row>
